--- a/outputs/MASTER_AUDIT_DATA.xlsx
+++ b/outputs/MASTER_AUDIT_DATA.xlsx
@@ -622,16 +622,8 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>aaaaa</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>bbbb</t>
-        </is>
-      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -938,7 +930,7 @@
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -1126,11 +1118,7 @@
           <t>105500000.00</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Count: 3</t>
-        </is>
-      </c>
+      <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1186,11 +1174,7 @@
           <t>5000000.00</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Count: 1</t>
-        </is>
-      </c>
+      <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1210,11 +1194,7 @@
           <t>110500000.00</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Count: 4</t>
-        </is>
-      </c>
+      <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1234,11 +1214,7 @@
           <t>110500000.00</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Count: 4</t>
-        </is>
-      </c>
+      <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1914,172 +1890,160 @@
       <c r="V8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Typewise Total</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>124400.00</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>-6203624.00</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>8700000.00</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>1749188.00</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>SUMMARY</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Typewise Total</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>503000.00</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>-32334493.00</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>35000000.00</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>508399.00</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>SUMMARY</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Branchwise Total</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>627400.00</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>-38538117.00</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>43700000.00</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>2257587.00</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>SUMMARY</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr"/>
@@ -2130,11 +2094,7 @@
       <c r="R12" s="5" t="inlineStr"/>
       <c r="S12" s="5" t="inlineStr"/>
       <c r="T12" s="5" t="inlineStr"/>
-      <c r="U12" s="5" t="inlineStr">
-        <is>
-          <t>SUMMARY</t>
-        </is>
-      </c>
+      <c r="U12" s="5" t="inlineStr"/>
       <c r="V12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
